--- a/assets/models/Paytm.xlsx
+++ b/assets/models/Paytm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\startbootstrap-clean-blog-gh-pages\startbootstrap-clean-blog-gh-pages\assets\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3AEEB0F-F963-4FC6-ABBF-15B373B079E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A241F1F9-26BF-4489-8831-6009651814BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="4" xr2:uid="{E0B1C313-72C6-44D8-B4FF-58EBAD9627F7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="6" xr2:uid="{E0B1C313-72C6-44D8-B4FF-58EBAD9627F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -3878,7 +3878,7 @@
     <xf numFmtId="9" fontId="54" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="359">
+  <cellXfs count="357">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4335,7 +4335,6 @@
     <xf numFmtId="41" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -4382,7 +4381,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4453,6 +4451,66 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="185" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="49" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="190" fontId="51" fillId="10" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="190" fontId="51" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="190" fontId="7" fillId="10" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="190" fontId="7" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="192" fontId="55" fillId="14" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="192" fontId="55" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="192" fontId="55" fillId="14" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="192" fontId="59" fillId="17" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="192" fontId="60" fillId="17" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="192" fontId="59" fillId="17" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="192" fontId="56" fillId="15" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="192" fontId="56" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="192" fontId="56" fillId="15" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="192" fontId="56" fillId="15" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -4476,66 +4534,6 @@
     </xf>
     <xf numFmtId="192" fontId="57" fillId="16" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="192" fontId="56" fillId="15" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="192" fontId="56" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="192" fontId="56" fillId="15" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="192" fontId="55" fillId="14" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="192" fontId="55" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="192" fontId="55" fillId="14" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="192" fontId="59" fillId="17" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="192" fontId="60" fillId="17" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="192" fontId="59" fillId="17" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="190" fontId="51" fillId="10" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="190" fontId="51" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="190" fontId="7" fillId="10" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="190" fontId="7" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="49" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4935,31 +4933,31 @@
             <c:strLit>
               <c:ptCount val="9"/>
               <c:pt idx="0">
-                <c:v>200.00%</c:v>
+                <c:v>2</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>300.00%</c:v>
+                <c:v>3</c:v>
               </c:pt>
               <c:pt idx="2">
-                <c:v>400.00%</c:v>
+                <c:v>4</c:v>
               </c:pt>
               <c:pt idx="3">
-                <c:v>500.00%</c:v>
+                <c:v>5</c:v>
               </c:pt>
               <c:pt idx="4">
-                <c:v>600.00%</c:v>
+                <c:v>6</c:v>
               </c:pt>
               <c:pt idx="5">
-                <c:v>700.00%</c:v>
+                <c:v>7</c:v>
               </c:pt>
               <c:pt idx="6">
-                <c:v>800.00%</c:v>
+                <c:v>8</c:v>
               </c:pt>
               <c:pt idx="7">
-                <c:v>900.00%</c:v>
+                <c:v>9</c:v>
               </c:pt>
               <c:pt idx="8">
-                <c:v>1000.00%</c:v>
+                <c:v>10</c:v>
               </c:pt>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
@@ -5060,31 +5058,31 @@
             <c:strLit>
               <c:ptCount val="9"/>
               <c:pt idx="0">
-                <c:v>200.00%</c:v>
+                <c:v>2</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>300.00%</c:v>
+                <c:v>3</c:v>
               </c:pt>
               <c:pt idx="2">
-                <c:v>400.00%</c:v>
+                <c:v>4</c:v>
               </c:pt>
               <c:pt idx="3">
-                <c:v>500.00%</c:v>
+                <c:v>5</c:v>
               </c:pt>
               <c:pt idx="4">
-                <c:v>600.00%</c:v>
+                <c:v>6</c:v>
               </c:pt>
               <c:pt idx="5">
-                <c:v>700.00%</c:v>
+                <c:v>7</c:v>
               </c:pt>
               <c:pt idx="6">
-                <c:v>800.00%</c:v>
+                <c:v>8</c:v>
               </c:pt>
               <c:pt idx="7">
-                <c:v>900.00%</c:v>
+                <c:v>9</c:v>
               </c:pt>
               <c:pt idx="8">
-                <c:v>1000.00%</c:v>
+                <c:v>10</c:v>
               </c:pt>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
@@ -8709,18 +8707,18 @@
       <c r="A23" t="s">
         <v>257</v>
       </c>
-      <c r="B23" s="357" t="s">
+      <c r="B23" s="355" t="s">
         <v>258</v>
       </c>
-      <c r="C23" s="357"/>
-      <c r="D23" s="357" t="s">
+      <c r="C23" s="355"/>
+      <c r="D23" s="355" t="s">
         <v>259</v>
       </c>
-      <c r="E23" s="357"/>
-      <c r="F23" s="357" t="s">
+      <c r="E23" s="355"/>
+      <c r="F23" s="355" t="s">
         <v>260</v>
       </c>
-      <c r="G23" s="357"/>
+      <c r="G23" s="355"/>
       <c r="S23" t="s">
         <v>658</v>
       </c>
@@ -13000,37 +12998,37 @@
       </c>
     </row>
     <row r="271" spans="1:11" ht="119" x14ac:dyDescent="0.6">
-      <c r="A271" s="290" t="s">
+      <c r="A271" s="288" t="s">
         <v>806</v>
       </c>
-      <c r="B271" s="290" t="s">
+      <c r="B271" s="288" t="s">
         <v>807</v>
       </c>
-      <c r="C271" s="290" t="s">
+      <c r="C271" s="288" t="s">
         <v>808</v>
       </c>
-      <c r="D271" s="290" t="s">
+      <c r="D271" s="288" t="s">
         <v>809</v>
       </c>
-      <c r="E271" s="291" t="s">
+      <c r="E271" s="289" t="s">
         <v>810</v>
       </c>
-      <c r="F271" s="291" t="s">
+      <c r="F271" s="289" t="s">
         <v>811</v>
       </c>
-      <c r="G271" s="291" t="s">
+      <c r="G271" s="289" t="s">
         <v>812</v>
       </c>
-      <c r="H271" s="291" t="s">
+      <c r="H271" s="289" t="s">
         <v>813</v>
       </c>
-      <c r="I271" s="291" t="s">
+      <c r="I271" s="289" t="s">
         <v>814</v>
       </c>
-      <c r="J271" s="291" t="s">
+      <c r="J271" s="289" t="s">
         <v>815</v>
       </c>
-      <c r="K271" s="291" t="s">
+      <c r="K271" s="289" t="s">
         <v>816</v>
       </c>
     </row>
@@ -13041,7 +13039,7 @@
       <c r="B272" s="243" t="s">
         <v>818</v>
       </c>
-      <c r="C272" s="292" t="s">
+      <c r="C272" s="290" t="s">
         <v>20</v>
       </c>
       <c r="D272" s="243" t="s">
@@ -13076,7 +13074,7 @@
       <c r="B273" s="243" t="s">
         <v>820</v>
       </c>
-      <c r="C273" s="292" t="s">
+      <c r="C273" s="290" t="s">
         <v>20</v>
       </c>
       <c r="D273" s="243" t="s">
@@ -13111,7 +13109,7 @@
       <c r="B274" s="243" t="s">
         <v>822</v>
       </c>
-      <c r="C274" s="292" t="s">
+      <c r="C274" s="290" t="s">
         <v>20</v>
       </c>
       <c r="D274" s="243" t="s">
@@ -13146,7 +13144,7 @@
       <c r="B275" s="243" t="s">
         <v>824</v>
       </c>
-      <c r="C275" s="292" t="s">
+      <c r="C275" s="290" t="s">
         <v>20</v>
       </c>
       <c r="D275" s="243" t="s">
@@ -13181,7 +13179,7 @@
       <c r="B276" s="243" t="s">
         <v>826</v>
       </c>
-      <c r="C276" s="292" t="s">
+      <c r="C276" s="290" t="s">
         <v>20</v>
       </c>
       <c r="D276" s="243" t="s">
@@ -13216,7 +13214,7 @@
       <c r="B277" s="243" t="s">
         <v>828</v>
       </c>
-      <c r="C277" s="292" t="s">
+      <c r="C277" s="290" t="s">
         <v>20</v>
       </c>
       <c r="D277" s="243" t="s">
@@ -13251,7 +13249,7 @@
       <c r="B278" s="243" t="s">
         <v>830</v>
       </c>
-      <c r="C278" s="292" t="s">
+      <c r="C278" s="290" t="s">
         <v>20</v>
       </c>
       <c r="D278" s="243" t="s">
@@ -13286,7 +13284,7 @@
       <c r="B279" s="243" t="s">
         <v>832</v>
       </c>
-      <c r="C279" s="292" t="s">
+      <c r="C279" s="290" t="s">
         <v>20</v>
       </c>
       <c r="D279" s="243" t="s">
@@ -13321,7 +13319,7 @@
       <c r="B280" s="243" t="s">
         <v>834</v>
       </c>
-      <c r="C280" s="292" t="s">
+      <c r="C280" s="290" t="s">
         <v>20</v>
       </c>
       <c r="D280" s="243" t="s">
@@ -13356,7 +13354,7 @@
       <c r="B281" s="243" t="s">
         <v>836</v>
       </c>
-      <c r="C281" s="292" t="s">
+      <c r="C281" s="290" t="s">
         <v>20</v>
       </c>
       <c r="D281" s="243" t="s">
@@ -13391,7 +13389,7 @@
       <c r="B282" s="243" t="s">
         <v>838</v>
       </c>
-      <c r="C282" s="292" t="s">
+      <c r="C282" s="290" t="s">
         <v>20</v>
       </c>
       <c r="D282" s="243" t="s">
@@ -13426,7 +13424,7 @@
       <c r="B283" s="243" t="s">
         <v>840</v>
       </c>
-      <c r="C283" s="292" t="s">
+      <c r="C283" s="290" t="s">
         <v>20</v>
       </c>
       <c r="D283" s="243" t="s">
@@ -13461,7 +13459,7 @@
       <c r="B284" s="243" t="s">
         <v>842</v>
       </c>
-      <c r="C284" s="292" t="s">
+      <c r="C284" s="290" t="s">
         <v>20</v>
       </c>
       <c r="D284" s="243" t="s">
@@ -13496,7 +13494,7 @@
       <c r="B285" s="243" t="s">
         <v>844</v>
       </c>
-      <c r="C285" s="292" t="s">
+      <c r="C285" s="290" t="s">
         <v>20</v>
       </c>
       <c r="D285" s="243" t="s">
@@ -13531,7 +13529,7 @@
       <c r="B286" s="243" t="s">
         <v>846</v>
       </c>
-      <c r="C286" s="292" t="s">
+      <c r="C286" s="290" t="s">
         <v>20</v>
       </c>
       <c r="D286" s="243" t="s">
@@ -13566,7 +13564,7 @@
       <c r="B287" s="243" t="s">
         <v>848</v>
       </c>
-      <c r="C287" s="292" t="s">
+      <c r="C287" s="290" t="s">
         <v>20</v>
       </c>
       <c r="D287" s="243" t="s">
@@ -13601,7 +13599,7 @@
       <c r="B288" s="243" t="s">
         <v>850</v>
       </c>
-      <c r="C288" s="292" t="s">
+      <c r="C288" s="290" t="s">
         <v>20</v>
       </c>
       <c r="D288" s="243" t="s">
@@ -13755,7 +13753,7 @@
       <c r="K3" s="32">
         <v>1.84E-2</v>
       </c>
-      <c r="M3" s="324">
+      <c r="M3" s="322">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="N3">
@@ -13811,7 +13809,7 @@
         <f>(K3-1.11%)*1.5</f>
         <v>1.0949999999999998E-2</v>
       </c>
-      <c r="M4" s="324">
+      <c r="M4" s="322">
         <v>0.12</v>
       </c>
       <c r="N4">
@@ -14177,54 +14175,54 @@
       <c r="AI12" s="180"/>
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.35">
-      <c r="B13" s="358" t="s">
+      <c r="B13" s="356" t="s">
         <v>561</v>
       </c>
-      <c r="C13" s="358"/>
-      <c r="D13" s="358" t="s">
+      <c r="C13" s="356"/>
+      <c r="D13" s="356" t="s">
         <v>582</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358" t="s">
+      <c r="E13" s="356"/>
+      <c r="F13" s="356" t="s">
         <v>572</v>
       </c>
-      <c r="G13" s="358"/>
-      <c r="H13" s="358" t="s">
+      <c r="G13" s="356"/>
+      <c r="H13" s="356" t="s">
         <v>562</v>
       </c>
-      <c r="I13" s="358"/>
-      <c r="J13" s="358" t="s">
+      <c r="I13" s="356"/>
+      <c r="J13" s="356" t="s">
         <v>565</v>
       </c>
-      <c r="K13" s="358"/>
-      <c r="L13" s="358" t="s">
+      <c r="K13" s="356"/>
+      <c r="L13" s="356" t="s">
         <v>563</v>
       </c>
-      <c r="M13" s="358"/>
-      <c r="N13" s="358" t="s">
+      <c r="M13" s="356"/>
+      <c r="N13" s="356" t="s">
         <v>573</v>
       </c>
-      <c r="O13" s="358"/>
-      <c r="P13" s="358" t="s">
+      <c r="O13" s="356"/>
+      <c r="P13" s="356" t="s">
         <v>574</v>
       </c>
-      <c r="Q13" s="358"/>
-      <c r="R13" s="358" t="s">
+      <c r="Q13" s="356"/>
+      <c r="R13" s="356" t="s">
         <v>575</v>
       </c>
-      <c r="S13" s="358"/>
-      <c r="T13" s="358" t="s">
+      <c r="S13" s="356"/>
+      <c r="T13" s="356" t="s">
         <v>576</v>
       </c>
-      <c r="U13" s="358"/>
-      <c r="V13" s="358" t="s">
+      <c r="U13" s="356"/>
+      <c r="V13" s="356" t="s">
         <v>581</v>
       </c>
-      <c r="W13" s="358"/>
-      <c r="X13" s="358" t="s">
+      <c r="W13" s="356"/>
+      <c r="X13" s="356" t="s">
         <v>589</v>
       </c>
-      <c r="Y13" s="358"/>
+      <c r="Y13" s="356"/>
       <c r="Z13" s="146"/>
       <c r="AA13" s="146"/>
       <c r="AB13" s="146"/>
@@ -28950,87 +28948,87 @@
       <c r="J2" s="45"/>
       <c r="K2" s="45"/>
       <c r="L2" s="45"/>
-      <c r="M2" s="255"/>
+      <c r="M2" s="254"/>
       <c r="N2" s="45"/>
       <c r="O2" s="45"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
-      <c r="B3" s="256" t="s">
+      <c r="B3" s="255" t="s">
         <v>767</v>
       </c>
-      <c r="C3" s="257"/>
-      <c r="D3" s="256"/>
-      <c r="E3" s="256"/>
-      <c r="F3" s="256"/>
-      <c r="G3" s="256"/>
-      <c r="H3" s="256"/>
-      <c r="I3" s="256"/>
-      <c r="J3" s="256"/>
-      <c r="K3" s="258" t="s">
+      <c r="C3" s="256"/>
+      <c r="D3" s="255"/>
+      <c r="E3" s="255"/>
+      <c r="F3" s="255"/>
+      <c r="G3" s="255"/>
+      <c r="H3" s="255"/>
+      <c r="I3" s="255"/>
+      <c r="J3" s="255"/>
+      <c r="K3" s="257" t="s">
         <v>759</v>
       </c>
-      <c r="L3" s="256"/>
-      <c r="M3" s="259"/>
-      <c r="N3" s="256"/>
+      <c r="L3" s="255"/>
+      <c r="M3" s="258"/>
+      <c r="N3" s="255"/>
       <c r="O3" s="3"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
-      <c r="B4" s="256"/>
-      <c r="C4" s="257"/>
-      <c r="D4" s="256"/>
-      <c r="E4" s="256"/>
-      <c r="F4" s="256"/>
-      <c r="G4" s="256"/>
-      <c r="H4" s="256"/>
-      <c r="I4" s="256"/>
-      <c r="J4" s="256"/>
-      <c r="K4" s="259" t="s">
+      <c r="B4" s="255"/>
+      <c r="C4" s="256"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="258" t="s">
         <v>776</v>
       </c>
-      <c r="L4" s="256"/>
-      <c r="M4" s="259"/>
-      <c r="N4" s="256"/>
+      <c r="L4" s="255"/>
+      <c r="M4" s="258"/>
+      <c r="N4" s="255"/>
       <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="279"/>
-      <c r="B5" s="261"/>
-      <c r="C5" s="261">
+      <c r="A5" s="278"/>
+      <c r="B5" s="260"/>
+      <c r="C5" s="260">
         <v>2026</v>
       </c>
-      <c r="D5" s="261">
+      <c r="D5" s="260">
         <v>2027</v>
       </c>
-      <c r="E5" s="261">
+      <c r="E5" s="260">
         <v>2028</v>
       </c>
-      <c r="F5" s="261">
+      <c r="F5" s="260">
         <v>2029</v>
       </c>
-      <c r="G5" s="261">
+      <c r="G5" s="260">
         <v>2030</v>
       </c>
-      <c r="H5" s="261">
+      <c r="H5" s="260">
         <v>2031</v>
       </c>
-      <c r="I5" s="261">
+      <c r="I5" s="260">
         <v>2032</v>
       </c>
-      <c r="J5" s="261">
+      <c r="J5" s="260">
         <v>2033</v>
       </c>
-      <c r="K5" s="261">
+      <c r="K5" s="260">
         <v>2034</v>
       </c>
-      <c r="L5" s="261">
+      <c r="L5" s="260">
         <v>2035</v>
       </c>
-      <c r="M5" s="262" t="s">
+      <c r="M5" s="261" t="s">
         <v>760</v>
       </c>
-      <c r="N5" s="260"/>
+      <c r="N5" s="259"/>
       <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -29048,7 +29046,7 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
-      <c r="M6" s="256"/>
+      <c r="M6" s="255"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
     </row>
@@ -29097,10 +29095,10 @@
         <f>Schedules!S13*Schedules!S14</f>
         <v>72019761.358613893</v>
       </c>
-      <c r="M7" s="263" t="s">
+      <c r="M7" s="262" t="s">
         <v>777</v>
       </c>
-      <c r="N7" s="267">
+      <c r="N7" s="266">
         <f>((Schedules!S13*Schedules!S14)/(Schedules!J13*Schedules!J14))^(1/9)-1</f>
         <v>0.13068321521684023</v>
       </c>
@@ -29151,10 +29149,10 @@
         <f>Schedules!R36*Schedules!R35</f>
         <v>64254953.02765251</v>
       </c>
-      <c r="M8" s="263" t="s">
+      <c r="M8" s="262" t="s">
         <v>777</v>
       </c>
-      <c r="N8" s="267">
+      <c r="N8" s="266">
         <f>((Schedules!S36*Schedules!S35)/(Schedules!J35*Schedules!J36))^(1/9)-1</f>
         <v>0.15990483935115174</v>
       </c>
@@ -29205,10 +29203,10 @@
         <f>Schedules!S52</f>
         <v>40.314503709345715</v>
       </c>
-      <c r="M9" s="263" t="s">
+      <c r="M9" s="262" t="s">
         <v>777</v>
       </c>
-      <c r="N9" s="267">
+      <c r="N9" s="266">
         <f>(Schedules!S52/Schedules!J52)^(1/9)-1</f>
         <v>0.11528831552813479</v>
       </c>
@@ -29259,10 +29257,10 @@
         <f>Schedules!S68</f>
         <v>126.00000000000001</v>
       </c>
-      <c r="M10" s="263" t="s">
+      <c r="M10" s="262" t="s">
         <v>777</v>
       </c>
-      <c r="N10" s="267">
+      <c r="N10" s="266">
         <f>(Schedules!S68/Schedules!J68)^(1/9)-1</f>
         <v>5.6244412205185501E-2</v>
       </c>
@@ -29271,8 +29269,8 @@
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
-      <c r="M11" s="263"/>
-      <c r="N11" s="264"/>
+      <c r="M11" s="262"/>
+      <c r="N11" s="263"/>
       <c r="O11" s="3"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -29280,8 +29278,8 @@
       <c r="B12" s="70" t="s">
         <v>772</v>
       </c>
-      <c r="M12" s="263"/>
-      <c r="N12" s="264"/>
+      <c r="M12" s="262"/>
+      <c r="N12" s="263"/>
       <c r="O12" s="3"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
@@ -29329,10 +29327,10 @@
         <f>'Financial Statements'!S11</f>
         <v>385331.15019755653</v>
       </c>
-      <c r="M13" s="263" t="s">
+      <c r="M13" s="262" t="s">
         <v>777</v>
       </c>
-      <c r="N13" s="264">
+      <c r="N13" s="263">
         <f>('Financial Statements'!S11/'Financial Statements'!J11)^(1/9)-1</f>
         <v>0.18384271981467748</v>
       </c>
@@ -29383,10 +29381,10 @@
         <f>'Financial Statements'!S14</f>
         <v>264828.55327014951</v>
       </c>
-      <c r="M14" s="263" t="s">
+      <c r="M14" s="262" t="s">
         <v>777</v>
       </c>
-      <c r="N14" s="264">
+      <c r="N14" s="263">
         <f>('Financial Statements'!S14/'Financial Statements'!J14)^(1/9)-1</f>
         <v>0.20729744652395277</v>
       </c>
@@ -29437,10 +29435,10 @@
         <f>'Financial Statements'!S17</f>
         <v>116476.06044409022</v>
       </c>
-      <c r="M15" s="263" t="s">
+      <c r="M15" s="262" t="s">
         <v>777</v>
       </c>
-      <c r="N15" s="264">
+      <c r="N15" s="263">
         <f>('Financial Statements'!S17/'Financial Statements'!J17)^(1/9)-1</f>
         <v>0.41816213006616176</v>
       </c>
@@ -29491,10 +29489,10 @@
         <f>'Financial Statements'!S33</f>
         <v>102169.03590925878</v>
       </c>
-      <c r="M16" s="263" t="s">
+      <c r="M16" s="262" t="s">
         <v>777</v>
       </c>
-      <c r="N16" s="264">
+      <c r="N16" s="263">
         <f>('Financial Statements'!S33/'Financial Statements'!J33)^(1/9)-1</f>
         <v>0.3424706364639849</v>
       </c>
@@ -29503,8 +29501,8 @@
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
-      <c r="M17" s="263"/>
-      <c r="N17" s="264"/>
+      <c r="M17" s="262"/>
+      <c r="N17" s="263"/>
       <c r="O17" s="3"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
@@ -29522,7 +29520,7 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
-      <c r="M18" s="263"/>
+      <c r="M18" s="262"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
     </row>
@@ -29571,10 +29569,10 @@
         <f>'Financial Statements'!S36</f>
         <v>0.6872752258268604</v>
       </c>
-      <c r="M19" s="263" t="s">
+      <c r="M19" s="262" t="s">
         <v>789</v>
       </c>
-      <c r="N19" s="265" cm="1">
+      <c r="N19" s="264" cm="1">
         <f t="array" ref="N19">INDEX($D$5:$L$5,MATCH(TRUE,D19:L19&gt;65%,0))</f>
         <v>2030</v>
       </c>
@@ -29625,10 +29623,10 @@
         <f>'Financial Statements'!S37</f>
         <v>0.30227522582686028</v>
       </c>
-      <c r="M20" s="263" t="s">
+      <c r="M20" s="262" t="s">
         <v>790</v>
       </c>
-      <c r="N20" s="265" cm="1">
+      <c r="N20" s="264" cm="1">
         <f t="array" ref="N20">INDEX($D$5:$L$5,MATCH(TRUE,D20:L20&gt;20%,0))</f>
         <v>2029</v>
       </c>
@@ -29679,10 +29677,10 @@
         <f>'Financial Statements'!S38</f>
         <v>0.26514605906342492</v>
       </c>
-      <c r="M21" s="263" t="s">
+      <c r="M21" s="262" t="s">
         <v>790</v>
       </c>
-      <c r="N21" s="265" cm="1">
+      <c r="N21" s="264" cm="1">
         <f t="array" ref="N21">INDEX($D$5:$L$5,MATCH(TRUE,D21:L21&gt;20%,0))</f>
         <v>2032</v>
       </c>
@@ -29733,10 +29731,10 @@
         <f>'Financial Statements'!S39</f>
         <v>0.10867814007267708</v>
       </c>
-      <c r="M22" s="263" t="s">
+      <c r="M22" s="262" t="s">
         <v>791</v>
       </c>
-      <c r="N22" s="265" cm="1">
+      <c r="N22" s="264" cm="1">
         <f t="array" ref="N22">INDEX($D$5:$L$5,MATCH(TRUE,D22:L22&gt;10%,0))</f>
         <v>2032</v>
       </c>
@@ -29761,7 +29759,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
-      <c r="B24" s="256" t="s">
+      <c r="B24" s="255" t="s">
         <v>765</v>
       </c>
       <c r="C24" s="3"/>
@@ -29785,10 +29783,10 @@
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="272"/>
-      <c r="H25" s="269"/>
-      <c r="I25" s="269"/>
-      <c r="J25" s="269"/>
+      <c r="G25" s="271"/>
+      <c r="H25" s="268"/>
+      <c r="I25" s="268"/>
+      <c r="J25" s="268"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
@@ -29802,12 +29800,12 @@
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="276" t="s">
+      <c r="G26" s="275" t="s">
         <v>781</v>
       </c>
-      <c r="H26" s="277"/>
-      <c r="I26" s="271"/>
-      <c r="J26" s="271"/>
+      <c r="H26" s="276"/>
+      <c r="I26" s="270"/>
+      <c r="J26" s="270"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
@@ -29821,13 +29819,13 @@
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="274"/>
-      <c r="H27" s="353">
+      <c r="G27" s="273"/>
+      <c r="H27" s="324">
         <f>(Schedules!S47/Schedules!J47)^(1/9)-1</f>
         <v>0.1775795260364601</v>
       </c>
-      <c r="I27" s="353"/>
-      <c r="J27" s="269"/>
+      <c r="I27" s="324"/>
+      <c r="J27" s="268"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
@@ -29841,10 +29839,10 @@
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="275"/>
-      <c r="H28" s="353"/>
-      <c r="I28" s="353"/>
-      <c r="J28" s="269"/>
+      <c r="G28" s="274"/>
+      <c r="H28" s="324"/>
+      <c r="I28" s="324"/>
+      <c r="J28" s="268"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
@@ -29858,10 +29856,10 @@
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="272"/>
-      <c r="H29" s="353"/>
-      <c r="I29" s="353"/>
-      <c r="J29" s="269"/>
+      <c r="G29" s="271"/>
+      <c r="H29" s="324"/>
+      <c r="I29" s="324"/>
+      <c r="J29" s="268"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
@@ -29875,12 +29873,12 @@
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="272"/>
-      <c r="H30" s="345" t="s">
+      <c r="G30" s="271"/>
+      <c r="H30" s="325" t="s">
         <v>784</v>
       </c>
-      <c r="I30" s="345"/>
-      <c r="J30" s="269"/>
+      <c r="I30" s="325"/>
+      <c r="J30" s="268"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
@@ -29894,10 +29892,10 @@
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="272"/>
-      <c r="H31" s="278"/>
-      <c r="I31" s="278"/>
-      <c r="J31" s="269"/>
+      <c r="G31" s="271"/>
+      <c r="H31" s="277"/>
+      <c r="I31" s="277"/>
+      <c r="J31" s="268"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
@@ -29928,10 +29926,10 @@
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="272"/>
-      <c r="H33" s="269"/>
-      <c r="I33" s="269"/>
-      <c r="J33" s="269"/>
+      <c r="G33" s="271"/>
+      <c r="H33" s="268"/>
+      <c r="I33" s="268"/>
+      <c r="J33" s="268"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
@@ -29945,12 +29943,12 @@
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="276" t="s">
+      <c r="G34" s="275" t="s">
         <v>782</v>
       </c>
-      <c r="H34" s="271"/>
-      <c r="I34" s="271"/>
-      <c r="J34" s="271"/>
+      <c r="H34" s="270"/>
+      <c r="I34" s="270"/>
+      <c r="J34" s="270"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
@@ -29964,13 +29962,13 @@
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
-      <c r="G35" s="274"/>
-      <c r="H35" s="353">
+      <c r="G35" s="273"/>
+      <c r="H35" s="324">
         <f>(Schedules!S65/Schedules!J65)^(1/9)-1</f>
         <v>0.22869515300635124</v>
       </c>
-      <c r="I35" s="353"/>
-      <c r="J35" s="269"/>
+      <c r="I35" s="324"/>
+      <c r="J35" s="268"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
@@ -29984,10 +29982,10 @@
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
-      <c r="G36" s="275"/>
-      <c r="H36" s="353"/>
-      <c r="I36" s="353"/>
-      <c r="J36" s="269"/>
+      <c r="G36" s="274"/>
+      <c r="H36" s="324"/>
+      <c r="I36" s="324"/>
+      <c r="J36" s="268"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
@@ -30001,10 +29999,10 @@
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
-      <c r="G37" s="272"/>
-      <c r="H37" s="353"/>
-      <c r="I37" s="353"/>
-      <c r="J37" s="269"/>
+      <c r="G37" s="271"/>
+      <c r="H37" s="324"/>
+      <c r="I37" s="324"/>
+      <c r="J37" s="268"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
@@ -30018,12 +30016,12 @@
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
-      <c r="G38" s="272"/>
-      <c r="H38" s="345" t="s">
+      <c r="G38" s="271"/>
+      <c r="H38" s="325" t="s">
         <v>784</v>
       </c>
-      <c r="I38" s="345"/>
-      <c r="J38" s="269"/>
+      <c r="I38" s="325"/>
+      <c r="J38" s="268"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
@@ -30037,10 +30035,10 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
-      <c r="G39" s="272"/>
-      <c r="H39" s="278"/>
-      <c r="I39" s="278"/>
-      <c r="J39" s="269"/>
+      <c r="G39" s="271"/>
+      <c r="H39" s="277"/>
+      <c r="I39" s="277"/>
+      <c r="J39" s="268"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
@@ -30071,10 +30069,10 @@
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
-      <c r="G41" s="272"/>
-      <c r="H41" s="269"/>
-      <c r="I41" s="269"/>
-      <c r="J41" s="269"/>
+      <c r="G41" s="271"/>
+      <c r="H41" s="268"/>
+      <c r="I41" s="268"/>
+      <c r="J41" s="268"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -30088,12 +30086,12 @@
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
-      <c r="G42" s="276" t="s">
+      <c r="G42" s="275" t="s">
         <v>783</v>
       </c>
-      <c r="H42" s="271"/>
-      <c r="I42" s="271"/>
-      <c r="J42" s="271"/>
+      <c r="H42" s="270"/>
+      <c r="I42" s="270"/>
+      <c r="J42" s="270"/>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
@@ -30107,13 +30105,13 @@
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
-      <c r="G43" s="274"/>
-      <c r="H43" s="353">
+      <c r="G43" s="273"/>
+      <c r="H43" s="324">
         <f>(Schedules!S74/Schedules!J74)^(1/9)-1</f>
         <v>9.9134412889416046E-2</v>
       </c>
-      <c r="I43" s="353"/>
-      <c r="J43" s="269"/>
+      <c r="I43" s="324"/>
+      <c r="J43" s="268"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
@@ -30127,10 +30125,10 @@
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
-      <c r="G44" s="275"/>
-      <c r="H44" s="353"/>
-      <c r="I44" s="353"/>
-      <c r="J44" s="269"/>
+      <c r="G44" s="274"/>
+      <c r="H44" s="324"/>
+      <c r="I44" s="324"/>
+      <c r="J44" s="268"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
@@ -30144,10 +30142,10 @@
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
-      <c r="G45" s="272"/>
-      <c r="H45" s="353"/>
-      <c r="I45" s="353"/>
-      <c r="J45" s="269"/>
+      <c r="G45" s="271"/>
+      <c r="H45" s="324"/>
+      <c r="I45" s="324"/>
+      <c r="J45" s="268"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
@@ -30161,12 +30159,12 @@
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
-      <c r="G46" s="272"/>
-      <c r="H46" s="345" t="s">
+      <c r="G46" s="271"/>
+      <c r="H46" s="325" t="s">
         <v>784</v>
       </c>
-      <c r="I46" s="345"/>
-      <c r="J46" s="269"/>
+      <c r="I46" s="325"/>
+      <c r="J46" s="268"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
@@ -30180,10 +30178,10 @@
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
-      <c r="G47" s="272"/>
-      <c r="H47" s="269"/>
-      <c r="I47" s="269"/>
-      <c r="J47" s="269"/>
+      <c r="G47" s="271"/>
+      <c r="H47" s="268"/>
+      <c r="I47" s="268"/>
+      <c r="J47" s="268"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
@@ -30195,16 +30193,16 @@
       <c r="B48" s="47"/>
       <c r="C48" s="47"/>
       <c r="D48" s="47"/>
-      <c r="E48" s="280"/>
-      <c r="F48" s="280"/>
-      <c r="G48" s="280"/>
-      <c r="H48" s="280"/>
-      <c r="I48" s="280"/>
-      <c r="J48" s="280"/>
-      <c r="K48" s="280"/>
-      <c r="L48" s="280"/>
-      <c r="M48" s="280"/>
-      <c r="N48" s="280"/>
+      <c r="E48" s="279"/>
+      <c r="F48" s="279"/>
+      <c r="G48" s="279"/>
+      <c r="H48" s="279"/>
+      <c r="I48" s="279"/>
+      <c r="J48" s="279"/>
+      <c r="K48" s="279"/>
+      <c r="L48" s="279"/>
+      <c r="M48" s="279"/>
+      <c r="N48" s="279"/>
     </row>
     <row r="50" spans="1:15" ht="30" x14ac:dyDescent="0.6">
       <c r="A50" s="45"/>
@@ -30222,116 +30220,116 @@
       <c r="J50" s="45"/>
       <c r="K50" s="45"/>
       <c r="L50" s="45"/>
-      <c r="M50" s="255"/>
+      <c r="M50" s="254"/>
       <c r="N50" s="45"/>
       <c r="O50" s="45"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
-      <c r="B51" s="256" t="s">
+      <c r="B51" s="255" t="s">
         <v>799</v>
       </c>
-      <c r="C51" s="257"/>
-      <c r="D51" s="256" t="s">
+      <c r="C51" s="256"/>
+      <c r="D51" s="255" t="s">
         <v>856</v>
       </c>
-      <c r="E51" s="256"/>
-      <c r="F51" s="256"/>
-      <c r="G51" s="256"/>
-      <c r="H51" s="256"/>
-      <c r="I51" s="256"/>
-      <c r="J51" s="256"/>
-      <c r="K51" s="346" t="s">
+      <c r="E51" s="255"/>
+      <c r="F51" s="255"/>
+      <c r="G51" s="255"/>
+      <c r="H51" s="255"/>
+      <c r="I51" s="255"/>
+      <c r="J51" s="255"/>
+      <c r="K51" s="332" t="s">
         <v>792</v>
       </c>
-      <c r="L51" s="346"/>
-      <c r="M51" s="259" t="s">
+      <c r="L51" s="332"/>
+      <c r="M51" s="258" t="s">
         <v>776</v>
       </c>
-      <c r="N51" s="256"/>
+      <c r="N51" s="255"/>
       <c r="O51" s="3"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A52" s="308"/>
-      <c r="B52" s="309"/>
-      <c r="C52" s="310"/>
-      <c r="D52" s="311"/>
-      <c r="E52" s="311"/>
-      <c r="F52" s="311"/>
-      <c r="G52" s="311"/>
-      <c r="H52" s="311"/>
-      <c r="I52" s="311"/>
-      <c r="J52" s="311"/>
-      <c r="K52" s="311"/>
-      <c r="L52" s="311"/>
-      <c r="M52" s="312"/>
-      <c r="N52" s="311"/>
-      <c r="O52" s="311"/>
+      <c r="A52" s="306"/>
+      <c r="B52" s="307"/>
+      <c r="C52" s="308"/>
+      <c r="D52" s="309"/>
+      <c r="E52" s="309"/>
+      <c r="F52" s="309"/>
+      <c r="G52" s="309"/>
+      <c r="H52" s="309"/>
+      <c r="I52" s="309"/>
+      <c r="J52" s="309"/>
+      <c r="K52" s="309"/>
+      <c r="L52" s="309"/>
+      <c r="M52" s="310"/>
+      <c r="N52" s="309"/>
+      <c r="O52" s="309"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A53" s="308"/>
-      <c r="B53" s="309" t="s">
+      <c r="A53" s="306"/>
+      <c r="B53" s="307" t="s">
         <v>793</v>
       </c>
-      <c r="C53" s="310"/>
-      <c r="D53" s="347" t="str">
+      <c r="C53" s="308"/>
+      <c r="D53" s="333" t="str">
         <f>"Current market price of ₹"&amp; ROUND(ABS(D60),1)&amp;IF(D60&gt;B60," exceeds"," is below")&amp;" intrinsic value of ₹"&amp;ROUND(ABS(B60),1)&amp;" by "&amp;ROUND(ABS(D60-B60)/B60*100,0)&amp;"%"</f>
-        <v>Current market price of ₹1033.8 exceeds intrinsic value of ₹893.5 by 16%</v>
-      </c>
-      <c r="E53" s="347"/>
-      <c r="F53" s="347"/>
-      <c r="G53" s="347"/>
-      <c r="H53" s="347"/>
-      <c r="I53" s="347"/>
-      <c r="J53" s="347"/>
-      <c r="K53" s="347"/>
-      <c r="L53" s="347"/>
-      <c r="M53" s="348" t="str">
+        <v>Current market price of ₹1033.8 is below intrinsic value of ₹1079.7 by 4%</v>
+      </c>
+      <c r="E53" s="333"/>
+      <c r="F53" s="333"/>
+      <c r="G53" s="333"/>
+      <c r="H53" s="333"/>
+      <c r="I53" s="333"/>
+      <c r="J53" s="333"/>
+      <c r="K53" s="333"/>
+      <c r="L53" s="333"/>
+      <c r="M53" s="326" t="str">
         <f>IF(D60&gt;B60,"OVERVALUED","UNDERVALUED")</f>
-        <v>OVERVALUED</v>
-      </c>
-      <c r="N53" s="311"/>
-      <c r="O53" s="311"/>
+        <v>UNDERVALUED</v>
+      </c>
+      <c r="N53" s="309"/>
+      <c r="O53" s="309"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A54" s="308"/>
-      <c r="B54" s="309" t="s">
+      <c r="A54" s="306"/>
+      <c r="B54" s="307" t="s">
         <v>766</v>
       </c>
-      <c r="C54" s="308"/>
-      <c r="D54" s="347"/>
-      <c r="E54" s="347"/>
-      <c r="F54" s="347"/>
-      <c r="G54" s="347"/>
-      <c r="H54" s="347"/>
-      <c r="I54" s="347"/>
-      <c r="J54" s="347"/>
-      <c r="K54" s="347"/>
-      <c r="L54" s="347"/>
-      <c r="M54" s="348"/>
-      <c r="N54" s="308"/>
-      <c r="O54" s="308"/>
+      <c r="C54" s="306"/>
+      <c r="D54" s="333"/>
+      <c r="E54" s="333"/>
+      <c r="F54" s="333"/>
+      <c r="G54" s="333"/>
+      <c r="H54" s="333"/>
+      <c r="I54" s="333"/>
+      <c r="J54" s="333"/>
+      <c r="K54" s="333"/>
+      <c r="L54" s="333"/>
+      <c r="M54" s="326"/>
+      <c r="N54" s="306"/>
+      <c r="O54" s="306"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A55" s="308"/>
-      <c r="B55" s="309"/>
-      <c r="C55" s="308"/>
-      <c r="D55" s="308"/>
-      <c r="E55" s="308"/>
-      <c r="F55" s="308"/>
-      <c r="G55" s="308"/>
-      <c r="H55" s="308"/>
-      <c r="I55" s="308"/>
-      <c r="J55" s="308"/>
-      <c r="K55" s="308"/>
-      <c r="L55" s="308"/>
-      <c r="M55" s="308"/>
-      <c r="N55" s="308"/>
-      <c r="O55" s="308"/>
+      <c r="A55" s="306"/>
+      <c r="B55" s="307"/>
+      <c r="C55" s="306"/>
+      <c r="D55" s="306"/>
+      <c r="E55" s="306"/>
+      <c r="F55" s="306"/>
+      <c r="G55" s="306"/>
+      <c r="H55" s="306"/>
+      <c r="I55" s="306"/>
+      <c r="J55" s="306"/>
+      <c r="K55" s="306"/>
+      <c r="L55" s="306"/>
+      <c r="M55" s="306"/>
+      <c r="N55" s="306"/>
+      <c r="O55" s="306"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
-      <c r="B57" s="282"/>
+      <c r="B57" s="280"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -30348,241 +30346,241 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
-      <c r="B58" s="272"/>
+      <c r="B58" s="271"/>
       <c r="C58" s="3"/>
-      <c r="D58" s="288"/>
-      <c r="E58" s="269"/>
-      <c r="G58" s="288"/>
-      <c r="H58" s="269"/>
-      <c r="J58" s="288"/>
-      <c r="K58" s="269"/>
-      <c r="M58" s="288"/>
-      <c r="N58" s="269"/>
+      <c r="D58" s="286"/>
+      <c r="E58" s="268"/>
+      <c r="G58" s="286"/>
+      <c r="H58" s="268"/>
+      <c r="J58" s="286"/>
+      <c r="K58" s="268"/>
+      <c r="M58" s="286"/>
+      <c r="N58" s="268"/>
       <c r="O58" s="3"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
-      <c r="B59" s="295" t="str">
+      <c r="B59" s="293" t="str">
         <f>Assumptions!H8&amp;" IV"</f>
         <v>Base Case Scenario IV</v>
       </c>
-      <c r="C59" s="294"/>
-      <c r="D59" s="273" t="s">
+      <c r="C59" s="292"/>
+      <c r="D59" s="272" t="s">
         <v>794</v>
       </c>
-      <c r="E59" s="270"/>
-      <c r="G59" s="273" t="s">
+      <c r="E59" s="269"/>
+      <c r="G59" s="272" t="s">
         <v>795</v>
       </c>
-      <c r="H59" s="270"/>
-      <c r="J59" s="273" t="s">
+      <c r="H59" s="269"/>
+      <c r="J59" s="272" t="s">
         <v>796</v>
       </c>
-      <c r="K59" s="270"/>
-      <c r="M59" s="273" t="s">
+      <c r="K59" s="269"/>
+      <c r="M59" s="272" t="s">
         <v>854</v>
       </c>
-      <c r="N59" s="270"/>
+      <c r="N59" s="269"/>
       <c r="O59" s="3"/>
     </row>
     <row r="60" spans="1:15" ht="20" x14ac:dyDescent="0.4">
       <c r="A60" s="3"/>
-      <c r="B60" s="297">
+      <c r="B60" s="295">
         <f>ROUND('DCF Valuation'!I34,1)</f>
-        <v>893.5</v>
+        <v>1079.7</v>
       </c>
       <c r="C60" s="3"/>
-      <c r="D60" s="349">
+      <c r="D60" s="327">
         <f>ROUND(Assumptions!P8,1)</f>
         <v>1033.8</v>
       </c>
-      <c r="E60" s="350"/>
-      <c r="G60" s="351">
+      <c r="E60" s="328"/>
+      <c r="G60" s="329">
         <f>ROUND(H66,1)</f>
         <v>569.6</v>
       </c>
-      <c r="H60" s="352"/>
-      <c r="J60" s="351">
+      <c r="H60" s="330"/>
+      <c r="J60" s="329">
         <f>H67</f>
         <v>1574.3</v>
       </c>
-      <c r="K60" s="352"/>
-      <c r="M60" s="351">
+      <c r="K60" s="330"/>
+      <c r="M60" s="329">
         <f>'Relative Valuation'!D36</f>
         <v>1116.7478194118537</v>
       </c>
-      <c r="N60" s="352"/>
+      <c r="N60" s="330"/>
       <c r="O60" s="3"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
-      <c r="B61" s="296" t="s">
+      <c r="B61" s="294" t="s">
         <v>780</v>
       </c>
       <c r="C61" s="45"/>
-      <c r="D61" s="275" t="s">
+      <c r="D61" s="274" t="s">
         <v>797</v>
       </c>
-      <c r="E61" s="271"/>
-      <c r="G61" s="289" t="s">
+      <c r="E61" s="270"/>
+      <c r="G61" s="287" t="s">
         <v>798</v>
       </c>
-      <c r="H61" s="271"/>
-      <c r="J61" s="289" t="s">
+      <c r="H61" s="270"/>
+      <c r="J61" s="287" t="s">
         <v>798</v>
       </c>
-      <c r="K61" s="271"/>
-      <c r="M61" s="289" t="s">
+      <c r="K61" s="270"/>
+      <c r="M61" s="287" t="s">
         <v>855</v>
       </c>
-      <c r="N61" s="271"/>
+      <c r="N61" s="270"/>
       <c r="O61" s="3"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
-      <c r="B62" s="272"/>
+      <c r="B62" s="271"/>
       <c r="C62" s="3"/>
-      <c r="D62" s="288"/>
-      <c r="E62" s="269"/>
-      <c r="G62" s="288"/>
-      <c r="H62" s="269"/>
-      <c r="J62" s="288"/>
-      <c r="K62" s="269"/>
-      <c r="M62" s="288"/>
-      <c r="N62" s="269"/>
+      <c r="D62" s="286"/>
+      <c r="E62" s="268"/>
+      <c r="G62" s="286"/>
+      <c r="H62" s="268"/>
+      <c r="J62" s="286"/>
+      <c r="K62" s="268"/>
+      <c r="M62" s="286"/>
+      <c r="N62" s="268"/>
       <c r="O62" s="3"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A63" s="283"/>
-      <c r="B63" s="284"/>
-      <c r="C63" s="283"/>
-      <c r="D63" s="283"/>
-      <c r="E63" s="283"/>
-      <c r="F63" s="283"/>
-      <c r="G63" s="283"/>
-      <c r="H63" s="283"/>
-      <c r="I63" s="283"/>
-      <c r="J63" s="283"/>
-      <c r="K63" s="283"/>
-      <c r="L63" s="283"/>
-      <c r="M63" s="283"/>
-      <c r="N63" s="283"/>
+      <c r="A63" s="281"/>
+      <c r="B63" s="282"/>
+      <c r="C63" s="281"/>
+      <c r="D63" s="281"/>
+      <c r="E63" s="281"/>
+      <c r="F63" s="281"/>
+      <c r="G63" s="281"/>
+      <c r="H63" s="281"/>
+      <c r="I63" s="281"/>
+      <c r="J63" s="281"/>
+      <c r="K63" s="281"/>
+      <c r="L63" s="281"/>
+      <c r="M63" s="281"/>
+      <c r="N63" s="281"/>
       <c r="O63" s="3"/>
     </row>
     <row r="65" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B65" s="340" t="s">
+      <c r="B65" s="331" t="s">
         <v>863</v>
       </c>
-      <c r="C65" s="340"/>
-      <c r="D65" s="340"/>
-      <c r="F65" s="341" t="s">
+      <c r="C65" s="331"/>
+      <c r="D65" s="331"/>
+      <c r="F65" s="337" t="s">
         <v>851</v>
       </c>
-      <c r="G65" s="341"/>
-      <c r="H65" s="313">
+      <c r="G65" s="337"/>
+      <c r="H65" s="311">
         <f>IF(Assumptions!H8="Base Case Scenario",'DCF Valuation'!I34,902.4)</f>
-        <v>893.48531272155356</v>
+        <v>1079.6563342207362</v>
       </c>
       <c r="I65" s="191"/>
-      <c r="J65" s="285" t="s">
+      <c r="J65" s="283" t="s">
         <v>801</v>
       </c>
-      <c r="K65" s="286"/>
-      <c r="L65" s="286"/>
-      <c r="M65" s="286"/>
-      <c r="N65" s="286"/>
+      <c r="K65" s="284"/>
+      <c r="L65" s="284"/>
+      <c r="M65" s="284"/>
+      <c r="N65" s="284"/>
     </row>
     <row r="66" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B66" s="316"/>
-      <c r="C66" s="317"/>
-      <c r="D66" s="318"/>
-      <c r="F66" s="341" t="s">
+      <c r="B66" s="314"/>
+      <c r="C66" s="315"/>
+      <c r="D66" s="316"/>
+      <c r="F66" s="337" t="s">
         <v>861</v>
       </c>
-      <c r="G66" s="341"/>
-      <c r="H66" s="314">
+      <c r="G66" s="337"/>
+      <c r="H66" s="312">
         <f>IF(Assumptions!H8="Bear Case Scenario",'DCF Valuation'!I34,569.6)</f>
         <v>569.6</v>
       </c>
-      <c r="J66" s="287"/>
-      <c r="K66" s="285" t="s">
+      <c r="J66" s="285"/>
+      <c r="K66" s="283" t="s">
         <v>800</v>
       </c>
-      <c r="L66" s="285" t="s">
+      <c r="L66" s="283" t="s">
         <v>804</v>
       </c>
-      <c r="M66" s="285" t="s">
+      <c r="M66" s="283" t="s">
         <v>802</v>
       </c>
-      <c r="N66" s="285" t="s">
+      <c r="N66" s="283" t="s">
         <v>803</v>
       </c>
     </row>
     <row r="67" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B67" s="337" t="s">
+      <c r="B67" s="334" t="s">
         <v>866</v>
       </c>
-      <c r="C67" s="338"/>
-      <c r="D67" s="339"/>
-      <c r="F67" s="341" t="s">
+      <c r="C67" s="335"/>
+      <c r="D67" s="336"/>
+      <c r="F67" s="337" t="s">
         <v>862</v>
       </c>
-      <c r="G67" s="341"/>
-      <c r="H67" s="315">
+      <c r="G67" s="337"/>
+      <c r="H67" s="313">
         <f>IF(Assumptions!H8="Bull Case Scenario",'DCF Valuation'!I34,1574.3)</f>
         <v>1574.3</v>
       </c>
-      <c r="J67" s="285" t="s">
+      <c r="J67" s="283" t="s">
         <v>561</v>
       </c>
-      <c r="K67" s="298">
+      <c r="K67" s="296">
         <f>'Raw Data'!F290/'Raw Data'!G290</f>
         <v>8.396194926568759</v>
       </c>
-      <c r="L67" s="298">
+      <c r="L67" s="296">
         <f>'Raw Data'!F290/'Raw Data'!J290</f>
         <v>127.90677966101696</v>
       </c>
-      <c r="M67" s="298">
+      <c r="M67" s="296">
         <f>'Raw Data'!E290/'Raw Data'!G290</f>
         <v>6.7242990654205617</v>
       </c>
-      <c r="N67" s="298">
+      <c r="N67" s="296">
         <f>'Raw Data'!E290/'Raw Data'!I290</f>
         <v>112.96822429906543</v>
       </c>
     </row>
     <row r="68" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B68" s="334" t="s">
+      <c r="B68" s="341" t="s">
         <v>867</v>
       </c>
-      <c r="C68" s="335"/>
-      <c r="D68" s="336"/>
+      <c r="C68" s="342"/>
+      <c r="D68" s="343"/>
     </row>
     <row r="69" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B69" s="334" t="s">
+      <c r="B69" s="341" t="s">
         <v>868</v>
       </c>
-      <c r="C69" s="335"/>
-      <c r="D69" s="336"/>
-      <c r="F69" s="340" t="s">
+      <c r="C69" s="342"/>
+      <c r="D69" s="343"/>
+      <c r="F69" s="331" t="s">
         <v>864</v>
       </c>
-      <c r="G69" s="340"/>
-      <c r="H69" s="340"/>
-      <c r="J69" s="299" t="s">
+      <c r="G69" s="331"/>
+      <c r="H69" s="331"/>
+      <c r="J69" s="297" t="s">
         <v>805</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B70" s="334" t="s">
+      <c r="B70" s="341" t="s">
         <v>869</v>
       </c>
-      <c r="C70" s="335"/>
-      <c r="D70" s="336"/>
-      <c r="F70" s="342"/>
-      <c r="G70" s="342"/>
-      <c r="H70" s="342"/>
+      <c r="C70" s="342"/>
+      <c r="D70" s="343"/>
+      <c r="F70" s="338"/>
+      <c r="G70" s="338"/>
+      <c r="H70" s="338"/>
       <c r="J70" s="70" t="s">
         <v>630</v>
       </c>
@@ -30604,14 +30602,14 @@
       </c>
     </row>
     <row r="71" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B71" s="316"/>
-      <c r="C71" s="317"/>
-      <c r="D71" s="319"/>
-      <c r="F71" s="342" t="s">
+      <c r="B71" s="314"/>
+      <c r="C71" s="315"/>
+      <c r="D71" s="317"/>
+      <c r="F71" s="338" t="s">
         <v>885</v>
       </c>
-      <c r="G71" s="342"/>
-      <c r="H71" s="342"/>
+      <c r="G71" s="338"/>
+      <c r="H71" s="338"/>
       <c r="J71" s="70" t="s">
         <v>631</v>
       </c>
@@ -30633,16 +30631,16 @@
       </c>
     </row>
     <row r="72" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B72" s="337" t="s">
+      <c r="B72" s="334" t="s">
         <v>870</v>
       </c>
-      <c r="C72" s="338"/>
-      <c r="D72" s="339"/>
-      <c r="F72" s="342" t="s">
+      <c r="C72" s="335"/>
+      <c r="D72" s="336"/>
+      <c r="F72" s="338" t="s">
         <v>886</v>
       </c>
-      <c r="G72" s="342"/>
-      <c r="H72" s="342"/>
+      <c r="G72" s="338"/>
+      <c r="H72" s="338"/>
       <c r="J72" s="70" t="s">
         <v>632</v>
       </c>
@@ -30664,16 +30662,16 @@
       </c>
     </row>
     <row r="73" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B73" s="334" t="s">
+      <c r="B73" s="341" t="s">
         <v>871</v>
       </c>
-      <c r="C73" s="335"/>
-      <c r="D73" s="336"/>
-      <c r="F73" s="342" t="s">
+      <c r="C73" s="342"/>
+      <c r="D73" s="343"/>
+      <c r="F73" s="338" t="s">
         <v>887</v>
       </c>
-      <c r="G73" s="342"/>
-      <c r="H73" s="342"/>
+      <c r="G73" s="338"/>
+      <c r="H73" s="338"/>
       <c r="J73" s="70" t="s">
         <v>633</v>
       </c>
@@ -30695,16 +30693,16 @@
       </c>
     </row>
     <row r="74" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B74" s="334" t="s">
+      <c r="B74" s="341" t="s">
         <v>872</v>
       </c>
-      <c r="C74" s="335"/>
-      <c r="D74" s="336"/>
-      <c r="F74" s="342" t="s">
+      <c r="C74" s="342"/>
+      <c r="D74" s="343"/>
+      <c r="F74" s="338" t="s">
         <v>888</v>
       </c>
-      <c r="G74" s="342"/>
-      <c r="H74" s="342"/>
+      <c r="G74" s="338"/>
+      <c r="H74" s="338"/>
       <c r="J74" s="70" t="s">
         <v>634</v>
       </c>
@@ -30726,16 +30724,16 @@
       </c>
     </row>
     <row r="75" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B75" s="334" t="s">
+      <c r="B75" s="341" t="s">
         <v>873</v>
       </c>
-      <c r="C75" s="335"/>
-      <c r="D75" s="336"/>
-      <c r="F75" s="342" t="s">
+      <c r="C75" s="342"/>
+      <c r="D75" s="343"/>
+      <c r="F75" s="338" t="s">
         <v>889</v>
       </c>
-      <c r="G75" s="342"/>
-      <c r="H75" s="342"/>
+      <c r="G75" s="338"/>
+      <c r="H75" s="338"/>
       <c r="J75" s="70" t="s">
         <v>635</v>
       </c>
@@ -30757,14 +30755,14 @@
       </c>
     </row>
     <row r="76" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B76" s="316"/>
-      <c r="C76" s="317"/>
-      <c r="D76" s="319"/>
-      <c r="F76" s="342" t="s">
+      <c r="B76" s="314"/>
+      <c r="C76" s="315"/>
+      <c r="D76" s="317"/>
+      <c r="F76" s="338" t="s">
         <v>890</v>
       </c>
-      <c r="G76" s="342"/>
-      <c r="H76" s="342"/>
+      <c r="G76" s="338"/>
+      <c r="H76" s="338"/>
       <c r="J76" s="70" t="s">
         <v>636</v>
       </c>
@@ -30786,16 +30784,16 @@
       </c>
     </row>
     <row r="77" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B77" s="337" t="s">
+      <c r="B77" s="334" t="s">
         <v>874</v>
       </c>
-      <c r="C77" s="338"/>
-      <c r="D77" s="339"/>
-      <c r="F77" s="343" t="s">
+      <c r="C77" s="335"/>
+      <c r="D77" s="336"/>
+      <c r="F77" s="339" t="s">
         <v>891</v>
       </c>
-      <c r="G77" s="343"/>
-      <c r="H77" s="343"/>
+      <c r="G77" s="339"/>
+      <c r="H77" s="339"/>
       <c r="J77" s="70" t="s">
         <v>637</v>
       </c>
@@ -30817,14 +30815,14 @@
       </c>
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B78" s="334" t="s">
+      <c r="B78" s="341" t="s">
         <v>875</v>
       </c>
-      <c r="C78" s="335"/>
-      <c r="D78" s="336"/>
-      <c r="F78" s="344"/>
-      <c r="G78" s="344"/>
-      <c r="H78" s="344"/>
+      <c r="C78" s="342"/>
+      <c r="D78" s="343"/>
+      <c r="F78" s="340"/>
+      <c r="G78" s="340"/>
+      <c r="H78" s="340"/>
       <c r="J78" s="70" t="s">
         <v>638</v>
       </c>
@@ -30846,11 +30844,11 @@
       </c>
     </row>
     <row r="79" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B79" s="334" t="s">
+      <c r="B79" s="341" t="s">
         <v>876</v>
       </c>
-      <c r="C79" s="335"/>
-      <c r="D79" s="336"/>
+      <c r="C79" s="342"/>
+      <c r="D79" s="343"/>
       <c r="J79" s="70" t="s">
         <v>639</v>
       </c>
@@ -30872,16 +30870,16 @@
       </c>
     </row>
     <row r="80" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B80" s="326" t="s">
+      <c r="B80" s="344" t="s">
         <v>877</v>
       </c>
-      <c r="C80" s="326"/>
-      <c r="D80" s="326"/>
-      <c r="F80" s="340" t="s">
+      <c r="C80" s="344"/>
+      <c r="D80" s="344"/>
+      <c r="F80" s="331" t="s">
         <v>865</v>
       </c>
-      <c r="G80" s="340"/>
-      <c r="H80" s="340"/>
+      <c r="G80" s="331"/>
+      <c r="H80" s="331"/>
       <c r="J80" s="70" t="s">
         <v>640</v>
       </c>
@@ -30903,12 +30901,12 @@
       </c>
     </row>
     <row r="81" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B81" s="316"/>
-      <c r="C81" s="317"/>
-      <c r="D81" s="319"/>
-      <c r="F81" s="321"/>
-      <c r="G81" s="322"/>
-      <c r="H81" s="323"/>
+      <c r="B81" s="314"/>
+      <c r="C81" s="315"/>
+      <c r="D81" s="317"/>
+      <c r="F81" s="319"/>
+      <c r="G81" s="320"/>
+      <c r="H81" s="321"/>
       <c r="J81" s="70" t="s">
         <v>641</v>
       </c>
@@ -30930,14 +30928,14 @@
       </c>
     </row>
     <row r="82" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B82" s="327"/>
-      <c r="C82" s="328"/>
-      <c r="D82" s="329"/>
-      <c r="F82" s="320" t="s">
+      <c r="B82" s="345"/>
+      <c r="C82" s="346"/>
+      <c r="D82" s="347"/>
+      <c r="F82" s="318" t="s">
         <v>878</v>
       </c>
-      <c r="G82" s="320"/>
-      <c r="H82" s="320"/>
+      <c r="G82" s="318"/>
+      <c r="H82" s="318"/>
       <c r="J82" s="70" t="s">
         <v>642</v>
       </c>
@@ -30959,14 +30957,14 @@
       </c>
     </row>
     <row r="83" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B83" s="327"/>
-      <c r="C83" s="328"/>
-      <c r="D83" s="329"/>
-      <c r="F83" s="320" t="s">
+      <c r="B83" s="345"/>
+      <c r="C83" s="346"/>
+      <c r="D83" s="347"/>
+      <c r="F83" s="318" t="s">
         <v>879</v>
       </c>
-      <c r="G83" s="320"/>
-      <c r="H83" s="320"/>
+      <c r="G83" s="318"/>
+      <c r="H83" s="318"/>
       <c r="J83" s="70" t="s">
         <v>716</v>
       </c>
@@ -30988,14 +30986,14 @@
       </c>
     </row>
     <row r="84" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B84" s="327"/>
-      <c r="C84" s="328"/>
-      <c r="D84" s="329"/>
-      <c r="F84" s="320" t="s">
+      <c r="B84" s="345"/>
+      <c r="C84" s="346"/>
+      <c r="D84" s="347"/>
+      <c r="F84" s="318" t="s">
         <v>880</v>
       </c>
-      <c r="G84" s="320"/>
-      <c r="H84" s="320"/>
+      <c r="G84" s="318"/>
+      <c r="H84" s="318"/>
       <c r="J84" s="70" t="s">
         <v>717</v>
       </c>
@@ -31017,14 +31015,14 @@
       </c>
     </row>
     <row r="85" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B85" s="327"/>
-      <c r="C85" s="328"/>
-      <c r="D85" s="329"/>
-      <c r="F85" s="320" t="s">
+      <c r="B85" s="345"/>
+      <c r="C85" s="346"/>
+      <c r="D85" s="347"/>
+      <c r="F85" s="318" t="s">
         <v>881</v>
       </c>
-      <c r="G85" s="320"/>
-      <c r="H85" s="320"/>
+      <c r="G85" s="318"/>
+      <c r="H85" s="318"/>
       <c r="J85" s="70" t="s">
         <v>718</v>
       </c>
@@ -31046,14 +31044,14 @@
       </c>
     </row>
     <row r="86" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B86" s="327"/>
-      <c r="C86" s="328"/>
-      <c r="D86" s="329"/>
-      <c r="F86" s="320" t="s">
+      <c r="B86" s="345"/>
+      <c r="C86" s="346"/>
+      <c r="D86" s="347"/>
+      <c r="F86" s="318" t="s">
         <v>882</v>
       </c>
-      <c r="G86" s="320"/>
-      <c r="H86" s="320"/>
+      <c r="G86" s="318"/>
+      <c r="H86" s="318"/>
       <c r="J86" s="70" t="s">
         <v>719</v>
       </c>
@@ -31075,89 +31073,87 @@
       </c>
     </row>
     <row r="87" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B87" s="327"/>
-      <c r="C87" s="328"/>
-      <c r="D87" s="329"/>
-      <c r="F87" s="320" t="s">
+      <c r="B87" s="345"/>
+      <c r="C87" s="346"/>
+      <c r="D87" s="347"/>
+      <c r="F87" s="318" t="s">
         <v>883</v>
       </c>
-      <c r="G87" s="320"/>
-      <c r="H87" s="320"/>
+      <c r="G87" s="318"/>
+      <c r="H87" s="318"/>
     </row>
     <row r="88" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B88" s="327"/>
-      <c r="C88" s="328"/>
-      <c r="D88" s="329"/>
-      <c r="F88" s="320" t="s">
+      <c r="B88" s="345"/>
+      <c r="C88" s="346"/>
+      <c r="D88" s="347"/>
+      <c r="F88" s="318" t="s">
         <v>884</v>
       </c>
-      <c r="G88" s="320"/>
-      <c r="H88" s="320"/>
-      <c r="I88" s="293"/>
-      <c r="J88" s="287" t="s">
+      <c r="G88" s="318"/>
+      <c r="H88" s="318"/>
+      <c r="I88" s="291"/>
+      <c r="J88" s="285" t="s">
         <v>852</v>
       </c>
-      <c r="K88" s="298">
+      <c r="K88" s="296">
         <f>AVERAGE(K70:K86)</f>
         <v>6.194036110376131</v>
       </c>
-      <c r="L88" s="298">
+      <c r="L88" s="296">
         <f>AVERAGE(L70:L86)</f>
         <v>161.25600589453242</v>
       </c>
-      <c r="M88" s="298">
+      <c r="M88" s="296">
         <f>AVERAGE(M70:M86)</f>
         <v>5.7673079458190637</v>
       </c>
-      <c r="N88" s="298">
+      <c r="N88" s="296">
         <f>AVERAGE(N70:N86)</f>
         <v>42.622988757724656</v>
       </c>
     </row>
     <row r="89" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B89" s="330"/>
-      <c r="C89" s="331"/>
-      <c r="D89" s="332"/>
-      <c r="F89" s="333"/>
-      <c r="G89" s="333"/>
-      <c r="H89" s="333"/>
-      <c r="J89" s="287" t="s">
+      <c r="B89" s="348"/>
+      <c r="C89" s="349"/>
+      <c r="D89" s="350"/>
+      <c r="F89" s="351"/>
+      <c r="G89" s="351"/>
+      <c r="H89" s="351"/>
+      <c r="J89" s="285" t="s">
         <v>853</v>
       </c>
-      <c r="K89" s="298">
+      <c r="K89" s="296">
         <f>MEDIAN(K70:K86)</f>
         <v>5.0762645914396884</v>
       </c>
-      <c r="L89" s="298">
+      <c r="L89" s="296">
         <f>MEDIAN(L70:L86)</f>
         <v>48.140221402214017</v>
       </c>
-      <c r="M89" s="298">
+      <c r="M89" s="296">
         <f>MEDIAN(M70:M86)</f>
         <v>4.5824902723735415</v>
       </c>
-      <c r="N89" s="298">
+      <c r="N89" s="296">
         <f>MEDIAN(N70:N86)</f>
         <v>33.562745098039215</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="H27:I29"/>
-    <mergeCell ref="H35:I37"/>
-    <mergeCell ref="H43:I45"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="M53:M54"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="M60:N60"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="D53:L54"/>
-    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D89"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B73:D73"/>
     <mergeCell ref="F69:H69"/>
     <mergeCell ref="F80:H80"/>
     <mergeCell ref="F65:G65"/>
@@ -31172,19 +31168,21 @@
     <mergeCell ref="F77:H77"/>
     <mergeCell ref="F70:H70"/>
     <mergeCell ref="F78:H78"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D89"/>
-    <mergeCell ref="F89:H89"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="D53:L54"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="M53:M54"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="M60:N60"/>
+    <mergeCell ref="H27:I29"/>
+    <mergeCell ref="H35:I37"/>
+    <mergeCell ref="H43:I45"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H38:I38"/>
   </mergeCells>
   <conditionalFormatting sqref="M53">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Undervalued">
@@ -31341,14 +31339,14 @@
       </c>
       <c r="J8" s="215" t="str">
         <f ca="1">"Stock price -"&amp;TEXT(TODAY()-1," dd/mm/yyyy")</f>
-        <v>Stock price - 12/06/2026</v>
+        <v>Stock price - 19/06/2026</v>
       </c>
       <c r="K8" s="211"/>
       <c r="L8" s="211"/>
       <c r="M8" s="211"/>
       <c r="N8" s="211"/>
       <c r="O8" s="216"/>
-      <c r="P8" s="268">
+      <c r="P8" s="267">
         <v>1033.8</v>
       </c>
       <c r="R8" s="183"/>
@@ -46687,19 +46685,19 @@
       <c r="D41" s="92"/>
       <c r="E41" s="93"/>
       <c r="F41" s="92"/>
-      <c r="G41" s="266"/>
-      <c r="H41" s="266"/>
-      <c r="I41" s="266"/>
-      <c r="J41" s="266"/>
-      <c r="K41" s="266"/>
-      <c r="L41" s="266"/>
-      <c r="M41" s="266"/>
-      <c r="N41" s="266"/>
-      <c r="O41" s="266"/>
-      <c r="P41" s="266"/>
-      <c r="Q41" s="266"/>
-      <c r="R41" s="266"/>
-      <c r="S41" s="266"/>
+      <c r="G41" s="265"/>
+      <c r="H41" s="265"/>
+      <c r="I41" s="265"/>
+      <c r="J41" s="265"/>
+      <c r="K41" s="265"/>
+      <c r="L41" s="265"/>
+      <c r="M41" s="265"/>
+      <c r="N41" s="265"/>
+      <c r="O41" s="265"/>
+      <c r="P41" s="265"/>
+      <c r="Q41" s="265"/>
+      <c r="R41" s="265"/>
+      <c r="S41" s="265"/>
     </row>
     <row r="42" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B42" s="84"/>
@@ -51425,35 +51423,35 @@
       </c>
       <c r="J19" s="31">
         <f t="shared" ref="J19:Q19" si="5">J54</f>
-        <v>0.12966674577104226</v>
+        <v>0.12869174577104225</v>
       </c>
       <c r="K19" s="31">
         <f t="shared" si="5"/>
-        <v>0.12902149637517907</v>
+        <v>0.12707149637517906</v>
       </c>
       <c r="L19" s="31">
         <f t="shared" si="5"/>
-        <v>0.12837624697931591</v>
+        <v>0.12545124697931592</v>
       </c>
       <c r="M19" s="31">
         <f t="shared" si="5"/>
-        <v>0.12773099758345272</v>
+        <v>0.12383099758345271</v>
       </c>
       <c r="N19" s="31">
         <f t="shared" si="5"/>
-        <v>0.12708574818758955</v>
+        <v>0.12221074818758956</v>
       </c>
       <c r="O19" s="31">
         <f t="shared" si="5"/>
-        <v>0.12644049879172636</v>
+        <v>0.12059049879172637</v>
       </c>
       <c r="P19" s="31">
         <f t="shared" si="5"/>
-        <v>0.1257952493958632</v>
+        <v>0.1189702493958632</v>
       </c>
       <c r="Q19" s="31">
         <f t="shared" si="5"/>
-        <v>0.12514999999999998</v>
+        <v>0.11734999999999998</v>
       </c>
       <c r="S19" s="27"/>
       <c r="T19" s="27"/>
@@ -51481,35 +51479,35 @@
       </c>
       <c r="J20" s="27">
         <f t="shared" ref="J20:Q20" si="6">1/(1+J$19)^J42</f>
-        <v>0.83258273135143146</v>
+        <v>0.83366378119087803</v>
       </c>
       <c r="K20" s="27">
         <f t="shared" si="6"/>
-        <v>0.7383197276210125</v>
+        <v>0.74151737793118999</v>
       </c>
       <c r="L20" s="27">
         <f t="shared" si="6"/>
-        <v>0.65525633149286555</v>
+        <v>0.66123616216588466</v>
       </c>
       <c r="M20" s="27">
         <f t="shared" si="6"/>
-        <v>0.58220397920425393</v>
+        <v>0.59135118307585899</v>
       </c>
       <c r="N20" s="27">
         <f t="shared" si="6"/>
-        <v>0.51771697485047219</v>
+        <v>0.53021446629535407</v>
       </c>
       <c r="O20" s="27">
         <f t="shared" si="6"/>
-        <v>0.46120747189636441</v>
+        <v>0.47708407139586084</v>
       </c>
       <c r="P20" s="27">
         <f t="shared" si="6"/>
-        <v>0.41120123678389164</v>
+        <v>0.43038878979433959</v>
       </c>
       <c r="Q20" s="27">
         <f t="shared" si="6"/>
-        <v>0.36703830581237479</v>
+        <v>0.38939602752650793</v>
       </c>
     </row>
     <row r="21" spans="2:27" x14ac:dyDescent="0.3">
@@ -51528,35 +51526,35 @@
       </c>
       <c r="J21" s="27">
         <f t="shared" si="7"/>
-        <v>0.78360881159164997</v>
+        <v>0.78496320899200911</v>
       </c>
       <c r="K21" s="27">
         <f t="shared" si="7"/>
-        <v>0.69485368863420371</v>
+        <v>0.69846653042298568</v>
       </c>
       <c r="L21" s="27">
         <f t="shared" si="7"/>
-        <v>0.61685666046117071</v>
+        <v>0.62329444051757488</v>
       </c>
       <c r="M21" s="27">
         <f t="shared" si="7"/>
-        <v>0.54824213546726552</v>
+        <v>0.55782113715210291</v>
       </c>
       <c r="N21" s="27">
         <f t="shared" si="7"/>
-        <v>0.48781848218015711</v>
+        <v>0.5006721754810356</v>
       </c>
       <c r="O21" s="27">
         <f t="shared" si="7"/>
-        <v>0.4345524536459473</v>
+        <v>0.45068328260783869</v>
       </c>
       <c r="P21" s="27">
         <f t="shared" si="7"/>
-        <v>0.38754729181457886</v>
+        <v>0.40686626384845825</v>
       </c>
       <c r="Q21" s="27">
         <f t="shared" si="7"/>
-        <v>0.34602396583137157</v>
+        <v>0.36838072648912445</v>
       </c>
     </row>
     <row r="22" spans="2:27" x14ac:dyDescent="0.3">
@@ -51575,35 +51573,35 @@
       </c>
       <c r="J22" s="253">
         <f t="shared" ref="J22:P22" si="8">J20*J18</f>
-        <v>7963.5477158326512</v>
+        <v>7973.8878197712129</v>
       </c>
       <c r="K22" s="253">
         <f t="shared" si="8"/>
-        <v>11303.928077837216</v>
+        <v>11352.885200032484</v>
       </c>
       <c r="L22" s="253">
         <f t="shared" si="8"/>
-        <v>14629.072128802114</v>
+        <v>14762.576179093878</v>
       </c>
       <c r="M22" s="253">
         <f t="shared" si="8"/>
-        <v>17222.960276854097</v>
+        <v>17493.556038051513</v>
       </c>
       <c r="N22" s="253">
         <f t="shared" si="8"/>
-        <v>21183.674725897439</v>
+        <v>21695.040600532953</v>
       </c>
       <c r="O22" s="253">
         <f t="shared" si="8"/>
-        <v>26218.300692143606</v>
+        <v>27120.839104921248</v>
       </c>
       <c r="P22" s="253">
         <f t="shared" si="8"/>
-        <v>26848.894777049434</v>
+        <v>28101.72318738158</v>
       </c>
       <c r="Q22" s="253">
         <f>Q20*Q18</f>
-        <v>27154.51154556149</v>
+        <v>28808.597788890074</v>
       </c>
     </row>
     <row r="23" spans="2:27" x14ac:dyDescent="0.3">
@@ -51628,16 +51626,16 @@
       <c r="G24" s="126"/>
       <c r="I24" s="18">
         <f>SUM(I22:Q22)</f>
-        <v>157676.89432726888</v>
-      </c>
-      <c r="L24" s="354" t="s">
+        <v>162461.11030596579</v>
+      </c>
+      <c r="L24" s="352" t="s">
         <v>533</v>
       </c>
-      <c r="M24" s="354"/>
-      <c r="N24" s="354"/>
-      <c r="O24" s="354"/>
-      <c r="P24" s="354"/>
-      <c r="Q24" s="354"/>
+      <c r="M24" s="352"/>
+      <c r="N24" s="352"/>
+      <c r="O24" s="352"/>
+      <c r="P24" s="352"/>
+      <c r="Q24" s="352"/>
     </row>
     <row r="25" spans="2:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
@@ -51650,17 +51648,17 @@
       <c r="G25" s="126"/>
       <c r="I25" s="160">
         <f>I40</f>
-        <v>241756.30818343678</v>
+        <v>356178.34674287622</v>
       </c>
       <c r="J25" s="35"/>
-      <c r="L25" s="355" t="s">
+      <c r="L25" s="353" t="s">
         <v>535</v>
       </c>
-      <c r="M25" s="355"/>
-      <c r="N25" s="355"/>
-      <c r="O25" s="355"/>
-      <c r="P25" s="355"/>
-      <c r="Q25" s="355"/>
+      <c r="M25" s="353"/>
+      <c r="N25" s="353"/>
+      <c r="O25" s="353"/>
+      <c r="P25" s="353"/>
+      <c r="Q25" s="353"/>
     </row>
     <row r="26" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="70" t="s">
@@ -51673,14 +51671,14 @@
       <c r="G26" s="34"/>
       <c r="I26" s="34">
         <f>I24+I25</f>
-        <v>399433.20251070568</v>
-      </c>
-      <c r="K26" s="356" t="s">
+        <v>518639.45704884198</v>
+      </c>
+      <c r="K26" s="354" t="s">
         <v>537</v>
       </c>
       <c r="L26" s="127">
         <f>I34</f>
-        <v>893.48531272155356</v>
+        <v>1079.6563342207362</v>
       </c>
       <c r="M26" s="184">
         <v>0.09</v>
@@ -51710,15 +51708,26 @@
         <f>Assumptions!H150</f>
         <v>44170</v>
       </c>
-      <c r="K27" s="356"/>
+      <c r="K27" s="354"/>
       <c r="L27" s="184">
-        <v>0.05</v>
-      </c>
-      <c r="M27" s="254"/>
-      <c r="N27" s="254"/>
-      <c r="O27" s="254"/>
-      <c r="P27" s="254"/>
-      <c r="Q27" s="254"/>
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="M27" s="69">
+        <f t="dataTable" ref="M27:Q31" dt2D="1" dtr="1" r1="I37" r2="I38"/>
+        <v>1269.7320871063532</v>
+      </c>
+      <c r="N27" s="69">
+        <v>1145.3422140333769</v>
+      </c>
+      <c r="O27" s="69">
+        <v>1005.5241396490236</v>
+      </c>
+      <c r="P27" s="69">
+        <v>938.02575891174968</v>
+      </c>
+      <c r="Q27" s="69">
+        <v>896.56246788742419</v>
+      </c>
       <c r="R27" s="35"/>
       <c r="S27" s="35"/>
     </row>
@@ -51733,17 +51742,27 @@
       <c r="G28" s="34"/>
       <c r="I28" s="34">
         <f>I26+I27</f>
-        <v>443603.20251070568</v>
-      </c>
-      <c r="K28" s="356"/>
+        <v>562809.45704884198</v>
+      </c>
+      <c r="K28" s="354"/>
       <c r="L28" s="184">
-        <v>5.5E-2</v>
-      </c>
-      <c r="M28" s="254"/>
-      <c r="N28" s="254"/>
-      <c r="O28" s="254"/>
-      <c r="P28" s="254"/>
-      <c r="Q28" s="254"/>
+        <v>6.7500000000000004E-2</v>
+      </c>
+      <c r="M28" s="69">
+        <v>1354.6053025364281</v>
+      </c>
+      <c r="N28" s="69">
+        <v>1203.4757654695311</v>
+      </c>
+      <c r="O28" s="69">
+        <v>1040.0304235864091</v>
+      </c>
+      <c r="P28" s="69">
+        <v>963.44650071622436</v>
+      </c>
+      <c r="Q28" s="69">
+        <v>917.12506365856859</v>
+      </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
@@ -51757,15 +51776,25 @@
         <f>-('Financial Statements'!I84+'Financial Statements'!I75+'Financial Statements'!I80)</f>
         <v>-1604</v>
       </c>
-      <c r="K29" s="356"/>
+      <c r="K29" s="354"/>
       <c r="L29" s="184">
-        <v>0.06</v>
-      </c>
-      <c r="M29" s="254"/>
-      <c r="N29" s="254"/>
-      <c r="O29" s="254"/>
-      <c r="P29" s="254"/>
-      <c r="Q29" s="254"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M29" s="69">
+        <v>1460.6968218240215</v>
+      </c>
+      <c r="N29" s="69">
+        <v>1273.2360271929163</v>
+      </c>
+      <c r="O29" s="73">
+        <v>1079.6563342207362</v>
+      </c>
+      <c r="P29" s="69">
+        <v>992.04483524625834</v>
+      </c>
+      <c r="Q29" s="69">
+        <v>939.97239229317347</v>
+      </c>
     </row>
     <row r="30" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
@@ -51779,15 +51808,25 @@
         <f>Assumptions!H149</f>
         <v>130400</v>
       </c>
-      <c r="K30" s="356"/>
+      <c r="K30" s="354"/>
       <c r="L30" s="184">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="M30" s="254"/>
-      <c r="N30" s="254"/>
-      <c r="O30" s="281"/>
-      <c r="P30" s="254"/>
-      <c r="Q30" s="254"/>
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="M30" s="69">
+        <v>1597.1002037652124</v>
+      </c>
+      <c r="N30" s="69">
+        <v>1358.4985692992752</v>
+      </c>
+      <c r="O30" s="69">
+        <v>1125.6325510464617</v>
+      </c>
+      <c r="P30" s="69">
+        <v>1024.4562810469633</v>
+      </c>
+      <c r="Q30" s="69">
+        <v>965.5076419436142</v>
+      </c>
       <c r="S30" s="182"/>
     </row>
     <row r="31" spans="2:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -51802,15 +51841,25 @@
         <f>Schedules!I342</f>
         <v>-296</v>
       </c>
-      <c r="K31" s="356"/>
+      <c r="K31" s="354"/>
       <c r="L31" s="184">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="M31" s="254"/>
-      <c r="N31" s="254"/>
-      <c r="O31" s="254"/>
-      <c r="P31" s="254"/>
-      <c r="Q31" s="254"/>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="M31" s="69">
+        <v>1778.9713796868009</v>
+      </c>
+      <c r="N31" s="69">
+        <v>1465.0767469322243</v>
+      </c>
+      <c r="O31" s="69">
+        <v>1179.6185617442648</v>
+      </c>
+      <c r="P31" s="69">
+        <v>1061.4979333906263</v>
+      </c>
+      <c r="Q31" s="69">
+        <v>994.23479780035973</v>
+      </c>
     </row>
     <row r="32" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B32" s="70" t="s">
@@ -51823,7 +51872,7 @@
       <c r="G32" s="34"/>
       <c r="I32" s="34">
         <f>I28+I29+I30+I31</f>
-        <v>572103.20251070568</v>
+        <v>691309.45704884198</v>
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
@@ -51852,21 +51901,21 @@
       <c r="O33" s="3"/>
     </row>
     <row r="34" spans="2:17" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="300" t="s">
+      <c r="B34" s="298" t="s">
         <v>545</v>
       </c>
-      <c r="C34" s="301"/>
-      <c r="D34" s="301"/>
-      <c r="E34" s="302"/>
-      <c r="F34" s="302"/>
-      <c r="G34" s="303"/>
-      <c r="H34" s="302"/>
-      <c r="I34" s="304">
+      <c r="C34" s="299"/>
+      <c r="D34" s="299"/>
+      <c r="E34" s="300"/>
+      <c r="F34" s="300"/>
+      <c r="G34" s="301"/>
+      <c r="H34" s="300"/>
+      <c r="I34" s="302">
         <f>I32/I33</f>
-        <v>893.48531272155356</v>
+        <v>1079.6563342207362</v>
       </c>
       <c r="J34" s="188"/>
-      <c r="K34" s="325"/>
+      <c r="K34" s="323"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
@@ -51938,7 +51987,7 @@
       <c r="F38" s="3"/>
       <c r="G38" s="124"/>
       <c r="I38" s="184">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="J38" s="3"/>
       <c r="K38" s="30"/>
@@ -51957,7 +52006,7 @@
       <c r="F39" s="3"/>
       <c r="I39" s="160">
         <f>Q22*(1+I38)/(I37-I38)</f>
-        <v>658667.78577334504</v>
+        <v>914694.35116060497</v>
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
@@ -51978,7 +52027,7 @@
       <c r="H40" s="90"/>
       <c r="I40" s="161">
         <f>I39*Q20</f>
-        <v>241756.30818343678</v>
+        <v>356178.34674287622</v>
       </c>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
@@ -52220,9 +52269,40 @@
       </c>
       <c r="C53" s="3"/>
       <c r="E53" s="3"/>
-      <c r="F53" s="162">
-        <f>Assumptions!P143</f>
+      <c r="F53" s="162"/>
+      <c r="I53" s="31">
         <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="J53" s="31">
+        <f>I53+($Q$53-$I$53)/COUNT($J$6:$Q$6)</f>
+        <v>2.7525000000000001E-2</v>
+      </c>
+      <c r="K53" s="31">
+        <f t="shared" ref="K53:P53" si="12">J53+($Q$53-$I$53)/COUNT($J$6:$Q$6)</f>
+        <v>2.6550000000000001E-2</v>
+      </c>
+      <c r="L53" s="31">
+        <f t="shared" si="12"/>
+        <v>2.5575000000000001E-2</v>
+      </c>
+      <c r="M53" s="31">
+        <f t="shared" si="12"/>
+        <v>2.46E-2</v>
+      </c>
+      <c r="N53" s="31">
+        <f t="shared" si="12"/>
+        <v>2.3625E-2</v>
+      </c>
+      <c r="O53" s="31">
+        <f t="shared" si="12"/>
+        <v>2.265E-2</v>
+      </c>
+      <c r="P53" s="31">
+        <f t="shared" si="12"/>
+        <v>2.1675E-2</v>
+      </c>
+      <c r="Q53" s="31">
+        <v>2.07E-2</v>
       </c>
     </row>
     <row r="54" spans="2:17" ht="14.5" x14ac:dyDescent="0.35">
@@ -52236,40 +52316,40 @@
       <c r="G54" s="136"/>
       <c r="H54" s="90"/>
       <c r="I54" s="120">
-        <f>$F$49+I50*$F$52+$F$53</f>
+        <f>$F$49+I50*$F$52+I53</f>
         <v>0.13031199516690542</v>
       </c>
       <c r="J54" s="120">
-        <f t="shared" ref="J54:Q54" si="12">$F$49+J50*$F$52+$F$53</f>
-        <v>0.12966674577104226</v>
+        <f t="shared" ref="J54:Q54" si="13">$F$49+J50*$F$52+J53</f>
+        <v>0.12869174577104225</v>
       </c>
       <c r="K54" s="120">
-        <f t="shared" si="12"/>
-        <v>0.12902149637517907</v>
+        <f t="shared" si="13"/>
+        <v>0.12707149637517906</v>
       </c>
       <c r="L54" s="120">
-        <f t="shared" si="12"/>
-        <v>0.12837624697931591</v>
+        <f t="shared" si="13"/>
+        <v>0.12545124697931592</v>
       </c>
       <c r="M54" s="120">
-        <f t="shared" si="12"/>
-        <v>0.12773099758345272</v>
+        <f t="shared" si="13"/>
+        <v>0.12383099758345271</v>
       </c>
       <c r="N54" s="120">
-        <f t="shared" si="12"/>
-        <v>0.12708574818758955</v>
+        <f t="shared" si="13"/>
+        <v>0.12221074818758956</v>
       </c>
       <c r="O54" s="120">
-        <f t="shared" si="12"/>
-        <v>0.12644049879172636</v>
+        <f t="shared" si="13"/>
+        <v>0.12059049879172637</v>
       </c>
       <c r="P54" s="120">
-        <f t="shared" si="12"/>
-        <v>0.1257952493958632</v>
+        <f t="shared" si="13"/>
+        <v>0.1189702493958632</v>
       </c>
       <c r="Q54" s="120">
-        <f t="shared" si="12"/>
-        <v>0.12514999999999998</v>
+        <f t="shared" si="13"/>
+        <v>0.11734999999999998</v>
       </c>
     </row>
     <row r="55" spans="2:17" x14ac:dyDescent="0.3">
@@ -53318,11 +53398,11 @@
       </c>
     </row>
     <row r="36" spans="2:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="305" t="s">
+      <c r="B36" s="303" t="s">
         <v>779</v>
       </c>
-      <c r="C36" s="306"/>
-      <c r="D36" s="307">
+      <c r="C36" s="304"/>
+      <c r="D36" s="305">
         <f>D35/Assumptions!P7</f>
         <v>1116.7478194118537</v>
       </c>
